--- a/results/job_matches_2026-03-15.xlsx
+++ b/results/job_matches_2026-03-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,87 +573,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>The Scoular Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f7e914015d23a8</t>
+          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Analytics</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Scoular Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
+          <t>https://www.indeed.com/viewjob?jk=f93244101a55d1cf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93244101a55d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5e72ec30486808c7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e72ec30486808c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a93392d862334858</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93392d862334858</t>
+          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ff807fd0f137bc</t>
+          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
+          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>DevOps Engineer – Azure Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -985,76 +985,6 @@
         </is>
       </c>
       <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>DevOps Engineer – Azure Platform</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Skyworks Solutions</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=be89e65f4dd09bb7</t>
         </is>

--- a/results/job_matches_2026-03-15.xlsx
+++ b/results/job_matches_2026-03-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,52 +573,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Analytics</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Scoular Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af94693dec12b68</t>
+          <t>https://www.indeed.com/viewjob?jk=f93244101a55d1cf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93244101a55d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5e72ec30486808c7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e72ec30486808c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a93392d862334858</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93392d862334858</t>
+          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Software Engineer III - LLM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,52 +731,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
+          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
+          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
+          <t>DevOps Engineer – Azure Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Azure Platform</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -950,41 +950,6 @@
         </is>
       </c>
       <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Skyworks Solutions</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=be89e65f4dd09bb7</t>
         </is>

--- a/results/job_matches_2026-03-15.xlsx
+++ b/results/job_matches_2026-03-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,35 +713,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - LLM</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, SQS, SNS, ECS, RDS, Azure, Scala</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c421e2dcdbd2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
         </is>
       </c>
     </row>
@@ -753,47 +753,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
+          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,69 +801,69 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Databricks/Python/SQL</t>
+          <t>DevOps Engineer – Azure Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff38445088e6dc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Azure Platform</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -915,41 +915,6 @@
         </is>
       </c>
       <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Skyworks Solutions</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=be89e65f4dd09bb7</t>
         </is>

--- a/results/job_matches_2026-03-15.xlsx
+++ b/results/job_matches_2026-03-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ELCOR Tax &amp; Accounting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1916e0848359ede0</t>
+          <t>https://www.indeed.com/viewjob?jk=05bc7b696fdd2052</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bc7b696fdd2052</t>
+          <t>https://www.indeed.com/viewjob?jk=f93244101a55d1cf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93244101a55d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5e72ec30486808c7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e72ec30486808c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a93392d862334858</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93392d862334858</t>
+          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
+          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
         </is>
       </c>
     </row>
@@ -718,47 +718,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
+          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>DevOps Engineer – Azure Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
+          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Azure Platform</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -880,41 +880,6 @@
         </is>
       </c>
       <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Skyworks Solutions</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=be89e65f4dd09bb7</t>
         </is>

--- a/results/job_matches_2026-03-15.xlsx
+++ b/results/job_matches_2026-03-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ochsner Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>14.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3a7fa88191eb9b</t>
+          <t>https://www.indeed.com/viewjob?jk=05bc7b696fdd2052</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bc7b696fdd2052</t>
+          <t>https://www.indeed.com/viewjob?jk=f93244101a55d1cf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93244101a55d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5e72ec30486808c7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e72ec30486808c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a93392d862334858</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93392d862334858</t>
+          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
+          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
         </is>
       </c>
     </row>
@@ -683,47 +683,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
+          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,69 +731,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>DevOps Engineer – Azure Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
+          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Azure Platform</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -845,41 +845,6 @@
         </is>
       </c>
       <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Skyworks Solutions</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=be89e65f4dd09bb7</t>
         </is>

--- a/results/job_matches_2026-03-15.xlsx
+++ b/results/job_matches_2026-03-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,87 +503,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93244101a55d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=11d5b4bae86c5d93</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Senior DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e72ec30486808c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c8be363a36eab12f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,234 +601,234 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93392d862334858</t>
+          <t>https://www.indeed.com/viewjob?jk=f93244101a55d1cf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
+          <t>https://www.indeed.com/viewjob?jk=5e72ec30486808c7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
+          <t>https://www.indeed.com/viewjob?jk=a93392d862334858</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Back End</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
+          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
+          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Azure Platform</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,15 +836,85 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DevOps Engineer – Azure Platform</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Skyworks Solutions</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=be89e65f4dd09bb7</t>
         </is>

--- a/results/job_matches_2026-03-15.xlsx
+++ b/results/job_matches_2026-03-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54d7b40c19de92ce</t>
+          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
         </is>
       </c>
     </row>
@@ -718,47 +718,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
+          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>DevOps Engineer – Azure Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
+          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Azure Platform</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -880,41 +880,6 @@
         </is>
       </c>
       <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Skyworks Solutions</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=be89e65f4dd09bb7</t>
         </is>

--- a/results/job_matches_2026-03-15.xlsx
+++ b/results/job_matches_2026-03-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,35 +643,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93392d862334858</t>
+          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
         </is>
       </c>
     </row>
@@ -683,47 +683,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
+          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Distributed Storage Software Developer Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,69 +731,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
+          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>DevOps Engineer – Azure Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
+          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer – Azure Platform</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -845,41 +845,6 @@
         </is>
       </c>
       <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Skyworks Solutions</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=be89e65f4dd09bb7</t>
         </is>

--- a/results/job_matches_2026-03-15.xlsx
+++ b/results/job_matches_2026-03-15.xlsx
@@ -643,35 +643,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
+          <t>https://www.indeed.com/viewjob?jk=a93392d862334858</t>
         </is>
       </c>
     </row>
@@ -683,47 +683,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
+          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Distributed Storage Software Developer Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, HDFS, Scala, CI/CD, Docker</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c54ab545ff541cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-15.xlsx
+++ b/results/job_matches_2026-03-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -815,41 +815,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Skyworks Solutions</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be89e65f4dd09bb7</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/job_matches_2026-03-15.xlsx
+++ b/results/job_matches_2026-03-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,41 +780,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DevOps Engineer – Azure Platform</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d27eb7b013426664</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/job_matches_2026-03-15.xlsx
+++ b/results/job_matches_2026-03-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,60 +608,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e72ec30486808c7</t>
+          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,110 +671,40 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93392d862334858</t>
+          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Pluto TV</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>West Hollywood, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior AWS Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
         </is>

--- a/results/job_matches_2026-03-15.xlsx
+++ b/results/job_matches_2026-03-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,68 +643,103 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Lodging by Liberty DBA Charter Furniture</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
+          <t>https://www.indeed.com/viewjob?jk=134952c8e2b4c531</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pluto TV</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>West Hollywood, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Plymouth Rock Assurance</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Boston, MA, US USA</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>10.4</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-01-14</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
         </is>

--- a/results/job_matches_2026-03-15.xlsx
+++ b/results/job_matches_2026-03-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,70 +468,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.6</v>
+        <v>25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bc7b696fdd2052</t>
+          <t>https://www.indeed.com/viewjob?jk=92a6b6e514fcadd1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Remote</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SportsBiz Group Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d5b4bae86c5d93</t>
+          <t>https://www.indeed.com/viewjob?jk=05bc7b696fdd2052</t>
         </is>
       </c>
     </row>
@@ -566,94 +566,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8be363a36eab12f</t>
+          <t>https://www.indeed.com/viewjob?jk=11d5b4bae86c5d93</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93244101a55d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c8be363a36eab12f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
+          <t>https://www.indeed.com/viewjob?jk=f93244101a55d1cf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lodging by Liberty DBA Charter Furniture</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,85 +661,50 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=134952c8e2b4c531</t>
+          <t>https://www.indeed.com/viewjob?jk=595247e429160094</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fae9461b0cd0dc68</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior AWS Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
         </is>
